--- a/data/costs.xlsx
+++ b/data/costs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Borz\Desktop\отчет вб для ии\себес\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Borz\Desktop\отчет вб для ии\себес\НОВЫЙ ФАЙЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB3EBFD1-827C-440A-8902-2E4B21036387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1B83B45-1A83-4626-B831-A2F6C0479544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{657CAAFD-6F34-4886-9497-F0E95152FD0A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>Артикул поставщика</t>
   </si>
@@ -165,6 +165,24 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>вамп джус</t>
+  </si>
+  <si>
+    <t>Комплекс для набора массы Vamp Juice 60 кап.</t>
+  </si>
+  <si>
+    <t>for test</t>
+  </si>
+  <si>
+    <t>Тестобустер For Test для буста теста и выносливости 120кап.</t>
+  </si>
+  <si>
+    <t>арг ол</t>
+  </si>
+  <si>
+    <t>Аргинин 120 капсулы для мужчин, Olimp ArgiPower 1500</t>
   </si>
 </sst>
 </file>
@@ -174,7 +192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +237,27 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF4A4A59"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF77767E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -240,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -248,6 +287,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -688,6 +730,9 @@
       <c r="C9" s="2">
         <v>1700</v>
       </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
       <c r="O9" t="s">
         <v>41</v>
       </c>
@@ -825,19 +870,37 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3700</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1700</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1450</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
@@ -901,5 +964,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>